--- a/daily_matches/job_matches_2026-04-03.xlsx
+++ b/daily_matches/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,210 +468,700 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS (Snowflake)</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD, Terraform</t>
+          <t>Generative AI, RAG, Kinesis, Dataflow, Docker, Kubernetes, Git, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66fc8bb22a057543</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Kinesis, Dataflow, Docker, Kubernetes, Git, Kafka, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, CI/CD, Jenkins, Terraform, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data and AI Scientist</t>
+          <t>Applied AI/ML - Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+          <t>Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, EC2, Glue, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a88357763607a0</t>
+          <t>https://www.indeed.com/viewjob?jk=017ad26b9882da44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Monetization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Git, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf70b255520936d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>McCarthy &amp; Holthus, LLP</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Azure ML, MLflow, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Health Business Solutions</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr Associate - Site Reliability Engineer - CIB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58f9d35de8c42965</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=665a6bf5b85e36f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d046aaf447ae132</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Mid Level</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>General Dynamics Mission Systems</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ae16a6d1d2cdb4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate - Payments</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, S3, Glue, Redshift, Redshift, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a833277a9485b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise | HPE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=addd96cd006b2629</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d65e7d342e4a7eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist - Decision Analytics, Supply Chain Economics</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46b58bbfab2becbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - LLM Systems &amp; RAG Optimization</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Texas Sports Academy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a986b83d78b06773</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lyra Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53871baee70d4748</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-03.xlsx
+++ b/daily_matches/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Data Engineer - AWS (Snowflake)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kinesis, Dataflow, Docker, Kubernetes, Git, Kafka, MySQL, Cassandra</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bcfb79ed1af62a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kinesis, Dataflow, Docker, Kubernetes, Git, Kafka, MySQL, Cassandra</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, CI/CD, Terraform, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior Machine Learning Engineer- Credit Karma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, CI/CD, Jenkins, Terraform, Kafka, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eceb4a922e2b88e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e171cbc1d705a35a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI/ML - Senior Associate</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, EC2, Glue, Python</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, FastAPI, Git, Databricks, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017ad26b9882da44</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Product Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist---Junior Level</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BRMS Global Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,497 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Azure ML, MLflow, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Machine Learning Operations</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Health Business Solutions</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr Associate - Site Reliability Engineer - CIB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58f9d35de8c42965</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=665a6bf5b85e36f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d046aaf447ae132</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Software Engineer - Mid Level</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>General Dynamics Mission Systems</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae16a6d1d2cdb4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Scientist Associate - Payments</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a833277a9485b6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27f251c7fd5857f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d65e7d342e4a7eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Scientist - Decision Analytics, Supply Chain Economics</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46b58bbfab2becbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer - LLM Systems &amp; RAG Optimization</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Texas Sports Academy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a986b83d78b06773</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Lyra Health</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53871baee70d4748</t>
+          <t>https://www.indeed.com/viewjob?jk=d59b2f9802d02546</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-03.xlsx
+++ b/daily_matches/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS (Snowflake)</t>
+          <t>Sr. GenAI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bcfb79ed1af62a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba750643ca3862d1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, CI/CD, Terraform, Git, Databricks, PySpark</t>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer- Credit Karma</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python, SQL</t>
+          <t>RAG, TensorFlow, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, MySQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e171cbc1d705a35a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>DoiT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, FastAPI, Git, Databricks, MongoDB, Python, R</t>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=d34c50efb08fc9ae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Product Software Engineer</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, S3, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,217 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9347a5ea2f79808</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist---Junior Level</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BRMS Global Systems</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Git, Snowflake, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>United States Cold Storage</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Git, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91cbf3cf7d588be8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Engineer - Agent</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d59b2f9802d02546</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7de025b26e7385af</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Legal AI Engineer - Konexo US</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e47f68752f3d35ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Partner Engineering and Science, Inc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7c6799038e2b3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Partner Engineering and Science, Inc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ea28981d311058e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-03.xlsx
+++ b/daily_matches/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. GenAI Engineer</t>
+          <t>Senior AI Engineer, ARIA Team</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba750643ca3862d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau</t>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, MySQL, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DoiT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34c50efb08fc9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=381ce3311c88f78a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Senior Data Science Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, S3, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a68a6863ceeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=7902c6122e6d8b03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, CI/CD, Git, Snowflake, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=96522324933a2c6e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Git, Snowflake, Python, SQL, R, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cbf3cf7d588be8</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer - Agent</t>
+          <t>Senior Agentic Ai Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Rebel Athletic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de025b26e7385af</t>
+          <t>https://www.indeed.com/viewjob?jk=f4aa7cb8d6c230a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Legal AI Engineer - Konexo US</t>
+          <t>MLOps Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, S3, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e47f68752f3d35ee</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Partner Engineering and Science, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Azure ML, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,532 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7c6799038e2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=96c2471ded2c5005</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Partner Engineering and Science, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Information Protection Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Integration</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Lake, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7259d80e187d5e6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer - Healthcare (Remote)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, S3, Glue, Athena, Data Lake, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BI Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Intralot</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Helena, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Databricks, PostgreSQL, MySQL, Tableau, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Decision Intelligence Engineer - Next Best Action</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Databricks, PySpark, Kafka, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=852f85116477d740</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer II</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, PyTorch, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f22458aab523e5ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, PyTorch, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c13f6112354b531</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea28981d311058e</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21217825059892e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kubernetes, Terraform, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a04ad3d9d68fb26a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Integration Engineer, People Technologies</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Apache Airflow, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85999bd4d8722530</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Dataflow, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-03.xlsx
+++ b/daily_matches/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, ARIA Team</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0592edfcbf764ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d42cab50adf39d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>AI/ML Subject Matter Expert</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, CI/CD, Jenkins, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=b92998f6163d730c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>SAP iXp Intern - AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, PyTorch, FastAPI, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=58867d031ae187a5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, Kafka</t>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381ce3311c88f78a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Science Analyst</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7902c6122e6d8b03</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Decision Support Tools Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96522324933a2c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e59233835448107e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=73bd875ae8e35052</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Agentic Ai Engineer</t>
+          <t>Associate Cloud Platform Engineer – Azure &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rebel Athletic</t>
+          <t>InvoiceCloud</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Python</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4aa7cb8d6c230a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdeac7c9af06806</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Healthcare (Remote)</t>
+          <t>Data Science Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Further</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, S3, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, R</t>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,567 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7737e9fd7ab8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=29f455b3068e9493</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c2471ded2c5005</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Saviynt Security Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Information Protection Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineering &amp; Integration</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Lake, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7259d80e187d5e6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Experian</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, S3, Glue, Athena, Data Lake, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Intralot</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Helena, MT, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, Databricks, PostgreSQL, MySQL, Tableau, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Decision Intelligence Engineer - Next Best Action</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Databricks, PySpark, Kafka, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=852f85116477d740</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, PyTorch, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f22458aab523e5ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Machine Learning Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, PyTorch, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c13f6112354b531</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21217825059892e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, Terraform, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a04ad3d9d68fb26a</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Integration Engineer, People Technologies</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CoreWeave</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Apache Airflow, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85999bd4d8722530</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>AECOM</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AECOM</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Dataflow, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=9034733d03fcdd62</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-03.xlsx
+++ b/daily_matches/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d42cab50adf39d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Subject Matter Expert</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Greenwich, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, CI/CD, Jenkins, Git, Databricks</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92998f6163d730c</t>
+          <t>https://www.indeed.com/viewjob?jk=df99f5f5e8e06342</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAP iXp Intern - AI Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, PyTorch, FastAPI, Docker, Git, Python</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58867d031ae187a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Decision Support Tools Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Matplotlib, Python</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e59233835448107e</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, CI/CD, Snowflake, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bd875ae8e35052</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0667d12fd02a29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Cloud Platform Engineer – Azure &amp; Kubernetes</t>
+          <t>Senior Solutions Architect, Financial Services Banking</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>InvoiceCloud</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, Git, Dask, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdeac7c9af06806</t>
+          <t>https://www.indeed.com/viewjob?jk=6f89060cba5d923b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Science Analyst</t>
+          <t>Test Infrastructure Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Further</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>Docker, Kubernetes, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f455b3068e9493</t>
+          <t>https://www.indeed.com/viewjob?jk=fbffd909088af5bf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer - Robotics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,122 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9034733d03fcdd62</t>
+          <t>https://www.indeed.com/viewjob?jk=325782f459e5a288</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bessemer Trust</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Woodbridge, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01259c8d95c97f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72682ccd3412d787</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=822f7d17849d04eb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-03.xlsx
+++ b/daily_matches/job_matches_2026-04-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
+          <t>https://www.indeed.com/viewjob?jk=389b18a3b6ff0c20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Scientist Intern</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Greenwich, NY, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df99f5f5e8e06342</t>
+          <t>https://www.indeed.com/viewjob?jk=8c2f82cf6d2e0ec8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Cognos Dashboard Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL</t>
+          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd36e63834048802</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Snowflake, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Snowflake, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Copilot, Dataflow, Apache Airflow, Git, Snowflake, Databricks, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, CI/CD, Snowflake, R</t>
+          <t>Generative AI, RAG, FastAPI, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0667d12fd02a29</t>
+          <t>https://www.indeed.com/viewjob?jk=066ee8a84c86df19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, Financial Services Banking</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, Git, Dask, Python, R</t>
+          <t>Generative AI, RAG, FastAPI, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f89060cba5d923b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6f174b51e0a259</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Test Infrastructure Development Engineer</t>
+          <t>Data Software Engineer III - ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbffd909088af5bf</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Robotics</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=325782f459e5a288</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd924e6731961bd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bessemer Trust</t>
+          <t>SecurityScorecard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01259c8d95c97f95</t>
+          <t>https://www.indeed.com/viewjob?jk=304a60cec71b6d11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AWS)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SecurityScorecard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,462 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72682ccd3412d787</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb5cfadc26c2f80</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Digital Health And Behavior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=798910955ab6473b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d0967ccce4e2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sundays For Dogs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8104425c291a204a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Technical Architect</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Soho Dragon</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, OpenCV, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74466a54a10b3b8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sarah Cannon Research Institute</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Keras, Git, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=822f7d17849d04eb</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Industrial Engineer (Operations Research)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MiTek</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chesterfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b4f9a09f6d5be86</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ce82e0d295a2453</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate - Payments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=133c1cfa0631b68e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Computer Vision Developer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Holland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5f2a63e272546a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Computer Vision Developer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73b287295bd00ef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Industry Architect â€“ Advertising &amp; Media</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=131c36cfddfa3b97</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceb2e4e043a1a0dc</t>
         </is>
       </c>
     </row>
